--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484597_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484597_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6975</v>
+        <v>5.0358</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9544</v>
+        <v>3.144</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7431</v>
+        <v>1.8918</v>
       </c>
       <c r="G2" t="n">
         <v>3.4529</v>
@@ -610,13 +610,13 @@
         <v>1.2828</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8389</v>
+        <v>1.1772</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6471</v>
+        <v>0.8367</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1918</v>
+        <v>0.3405</v>
       </c>
       <c r="V2" t="n">
         <v>0.9554</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.87</v>
+        <v>4.5077</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3133</v>
+        <v>3.9015</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5567</v>
+        <v>0.6062</v>
       </c>
       <c r="G3" t="n">
         <v>3.9125</v>
@@ -688,13 +688,13 @@
         <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2977</v>
+        <v>0.9355</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1154</v>
+        <v>0.7036</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1823</v>
+        <v>0.2319</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2566</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8133</v>
+        <v>2.9427</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7753</v>
+        <v>2.8303</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0381</v>
+        <v>0.1124</v>
       </c>
       <c r="G4" t="n">
         <v>2.4788</v>
@@ -766,13 +766,13 @@
         <v>0.5498</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3791</v>
+        <v>0.5085</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5671</v>
+        <v>0.6222</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.188</v>
+        <v>-0.1137</v>
       </c>
       <c r="V4" t="n">
         <v>0.3219</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9445</v>
+        <v>2.609</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1113</v>
+        <v>3.6023</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1668</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1883</v>
+        <v>2.496</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.0051</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5962</v>
+        <v>2.4909</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1671</v>
+        <v>2.623</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0837</v>
+        <v>1.2538</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0833</v>
+        <v>1.3692</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0213</v>
+        <v>-0.127</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4916</v>
+        <v>-1.2487</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5128</v>
+        <v>1.1217</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1227</v>
+        <v>0.1288</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3107</v>
+        <v>0.2779</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.188</v>
+        <v>-0.1492</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6335</v>
+        <v>1.267</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6335</v>
+        <v>2.5339</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>P. PAREJA ANDRES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7719</v>
+        <v>2.1376</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8602</v>
+        <v>-0.3794</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6321</v>
+        <v>2.517</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0408</v>
+        <v>1.5646</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6241</v>
+        <v>-0.0092</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4167</v>
+        <v>1.5738</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5336</v>
+        <v>0.7361</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2515</v>
+        <v>0.0276</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2821</v>
+        <v>0.7085</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4928</v>
+        <v>0.8285</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3726</v>
+        <v>-0.0368</v>
       </c>
       <c r="O6" t="n">
         <v>0.8653</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.2828</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.7489</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1951</v>
+        <v>0.0837</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8778</v>
+        <v>0.0445</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3172</v>
+        <v>0.0392</v>
       </c>
       <c r="V6" t="n">
-        <v>1.9005</v>
+        <v>1.5889</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5444</v>
+        <v>1.5889</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. PAREJA ANDRES</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7039</v>
+        <v>1.7856</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0113</v>
+        <v>1.8368</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7152</v>
+        <v>-0.0511</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5646</v>
+        <v>1.1883</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0092</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5738</v>
+        <v>0.5962</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7361</v>
+        <v>1.1671</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0276</v>
+        <v>1.0837</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7085</v>
+        <v>0.0833</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8285</v>
+        <v>0.0213</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0368</v>
+        <v>-0.4916</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8653</v>
+        <v>0.5128</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3501</v>
+        <v>-0.0362</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5875</v>
+        <v>0.0362</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2374</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5889</v>
+        <v>0.6335</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5889</v>
+        <v>0.6335</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>X. CORTINA CAMPOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3932</v>
+        <v>0.9805</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9564</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5631</v>
+        <v>0.355</v>
       </c>
       <c r="G8" t="n">
-        <v>2.496</v>
+        <v>0.4097</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0051</v>
+        <v>-0.8692</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4909</v>
+        <v>1.2789</v>
       </c>
       <c r="J8" t="n">
-        <v>2.623</v>
+        <v>0.4068</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2538</v>
+        <v>0.2818</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3692</v>
+        <v>0.125</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.127</v>
+        <v>0.0029</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2487</v>
+        <v>-1.151</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1217</v>
+        <v>1.1538</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0869</v>
+        <v>0.4817</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.368</v>
+        <v>0.2187</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7189</v>
+        <v>0.263</v>
       </c>
       <c r="V8" t="n">
-        <v>1.267</v>
+        <v>-0.6439</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SÁEZ GONZÁLEZ</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6251</v>
+        <v>0.6773</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6251</v>
+        <v>-1.2859</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1.9633</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6251</v>
+        <v>-1.0408</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-0.6241</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6251</v>
+        <v>-0.4167</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6251</v>
+        <v>-1.5336</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.2515</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6251</v>
+        <v>-1.2821</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.4928</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.3726</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.8653</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.1005</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.4521</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.6483</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.5444</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. CORTINA CAMPOS</t>
+          <t>J. SÁEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5601</v>
+        <v>0.6251</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1308</v>
+        <v>0.6251</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4293</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4097</v>
+        <v>0.6251</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2789</v>
+        <v>0.6251</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4068</v>
+        <v>0.6251</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2818</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.125</v>
+        <v>0.6251</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0029</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.151</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1538</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0613</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.276</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2082</v>
+        <v>0.45</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6311</v>
+        <v>-0.4387</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.8888</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3196</v>
@@ -1390,13 +1390,13 @@
         <v>0.5498</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.022</v>
+        <v>0.2198</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0551</v>
+        <v>0.1373</v>
       </c>
       <c r="U12" t="n">
-        <v>0.033</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. ALMONACID RUBIO</t>
+          <t>G. PARDO GALLENT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0491</v>
+        <v>0.2312</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5433</v>
+        <v>-0.9424</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4942</v>
+        <v>1.1736</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5826</v>
+        <v>0.3073</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8905</v>
+        <v>1.2369</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3079</v>
+        <v>-0.9296</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5245</v>
+        <v>-0.155</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.576</v>
+        <v>1.1271</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0515</v>
+        <v>-1.2821</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0581</v>
+        <v>0.4623</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3145</v>
+        <v>0.1098</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2564</v>
+        <v>0.3525</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5498</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
         <v>0.5498</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6276</v>
+        <v>-0.0315</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0188</v>
+        <v>-0.1931</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6464</v>
+        <v>0.1616</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6439</v>
+        <v>0.3219</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. PARDO GALLENT</t>
+          <t>A. ALMONACID RUBIO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.0382</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1897</v>
+        <v>-0.1587</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0993</v>
+        <v>0.197</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3073</v>
+        <v>-0.5826</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2369</v>
+        <v>-0.8905</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9296</v>
+        <v>0.3079</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.155</v>
+        <v>-0.5245</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1271</v>
+        <v>-0.576</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2821</v>
+        <v>0.0515</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4623</v>
+        <v>-0.0581</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1098</v>
+        <v>-0.3145</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3525</v>
+        <v>0.2564</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.5498</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3532</v>
+        <v>0.7149</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4404</v>
+        <v>0.3658</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0872</v>
+        <v>0.3492</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3219</v>
+        <v>-0.6439</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.5806</v>
+        <v>-6.2862</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.0643</v>
+        <v>-4.9681</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5163</v>
+        <v>-1.3181</v>
       </c>
       <c r="G15" t="n">
         <v>-2.8062</v>
@@ -1624,13 +1624,13 @@
         <v>0.3665</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.125</v>
+        <v>0.1693</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.129</v>
+        <v>-0.0328</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0039</v>
+        <v>0.2021</v>
       </c>
       <c r="V15" t="n">
         <v>-1.267</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>15.8429</v>
+        <v>16.7098</v>
       </c>
       <c r="E16" t="n">
-        <v>8.541999999999998</v>
+        <v>9.367600000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>7.301000000000001</v>
+        <v>7.342499999999998</v>
       </c>
       <c r="G16" t="n">
         <v>12.6613</v>
@@ -1702,16 +1702,16 @@
         <v>10.0793</v>
       </c>
       <c r="S16" t="n">
-        <v>4.585199999999999</v>
+        <v>5.452199999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6433</v>
+        <v>3.469100000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>1.9416</v>
+        <v>1.9831</v>
       </c>
       <c r="V16" t="n">
-        <v>3.177699999999999</v>
+        <v>3.1777</v>
       </c>
       <c r="W16" t="n">
         <v>10.1773</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.0891</v>
+        <v>5.9142</v>
       </c>
       <c r="E17" t="n">
-        <v>4.862</v>
+        <v>4.6697</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2271</v>
+        <v>1.2445</v>
       </c>
       <c r="G17" t="n">
         <v>2.2074</v>
@@ -1780,13 +1780,13 @@
         <v>2.7489</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3484</v>
+        <v>0.1735</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0332</v>
+        <v>-0.1591</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3152</v>
+        <v>0.3325</v>
       </c>
       <c r="V17" t="n">
         <v>2.6171</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.4264</v>
       </c>
       <c r="E18" t="n">
-        <v>1.403</v>
+        <v>1.1146</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8702</v>
+        <v>-0.6881</v>
       </c>
       <c r="G18" t="n">
         <v>0.632</v>
@@ -1858,13 +1858,13 @@
         <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2879</v>
+        <v>-0.3942</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1267</v>
+        <v>-0.1617</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4146</v>
+        <v>-0.2325</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2774</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0025</v>
+        <v>-0.6543</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6582</v>
+        <v>-0.5621</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3443</v>
+        <v>-0.0922</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0557</v>
@@ -1936,13 +1936,13 @@
         <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7794</v>
+        <v>-0.4312</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5324</v>
+        <v>-0.4363</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.247</v>
+        <v>0.0051</v>
       </c>
       <c r="V19" t="n">
         <v>-1.267</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2985</v>
+        <v>-0.8717</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5803</v>
+        <v>-0.4842</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.3875</v>
       </c>
       <c r="G20" t="n">
         <v>-3.2498</v>
@@ -2014,13 +2014,13 @@
         <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6292</v>
+        <v>-0.2023</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3688</v>
+        <v>-0.2726</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2604</v>
+        <v>0.0703</v>
       </c>
       <c r="V20" t="n">
         <v>3.8632</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.999</v>
+        <v>-1.0316</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3731</v>
+        <v>0.7577</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3721</v>
+        <v>-1.7893</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9989</v>
@@ -2092,13 +2092,13 @@
         <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8113</v>
+        <v>-0.8439</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8446</v>
+        <v>-0.46</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9667</v>
+        <v>-0.3839</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2047</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4726</v>
+        <v>-1.6945</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0185</v>
+        <v>-1.9224</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.454</v>
+        <v>0.2279</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5412</v>
@@ -2170,13 +2170,13 @@
         <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.921</v>
+        <v>-0.1429</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1485</v>
+        <v>-0.0524</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7724</v>
+        <v>-0.0905</v>
       </c>
       <c r="V22" t="n">
         <v>-0.0104</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5921</v>
+        <v>-2.9913</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.789</v>
+        <v>-1.3659</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8031</v>
+        <v>-1.6254</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9886</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5089</v>
+        <v>0.1097</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8409</v>
+        <v>0.264</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.332</v>
+        <v>-0.1542</v>
       </c>
       <c r="V23" t="n">
         <v>-2.212</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1456</v>
+        <v>-5.4725</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7374</v>
+        <v>-5.4489</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4082</v>
+        <v>-0.0236</v>
       </c>
       <c r="G24" t="n">
         <v>-2.9124</v>
@@ -2326,13 +2326,13 @@
         <v>2.1991</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1176</v>
+        <v>-0.4446</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7164</v>
+        <v>-0.428</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4012</v>
+        <v>-0.0166</v>
       </c>
       <c r="V24" t="n">
         <v>-2.482</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9546</v>
+        <v>-6.9037</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1558</v>
+        <v>-4.0596</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7989</v>
+        <v>-2.8441</v>
       </c>
       <c r="G25" t="n">
         <v>-4.7543</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1039</v>
+        <v>0.1548</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3318</v>
+        <v>-0.2356</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4357</v>
+        <v>0.3904</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2047</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.843</v>
+        <v>-13.279</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.301099999999999</v>
+        <v>-7.3011</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.5419</v>
+        <v>-5.9778</v>
       </c>
       <c r="G26" t="n">
         <v>-12.6615</v>
@@ -2482,13 +2482,13 @@
         <v>14.6606</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.585199999999999</v>
+        <v>-2.0211</v>
       </c>
       <c r="T26" t="n">
         <v>-1.9417</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.643400000000001</v>
+        <v>-0.07939999999999997</v>
       </c>
       <c r="V26" t="n">
         <v>-3.1779</v>
